--- a/public/downloads/MandalTowards2025.xlsx
+++ b/public/downloads/MandalTowards2025.xlsx
@@ -11,13 +11,14 @@
     <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
     <sheet name="anomaly" sheetId="3" r:id="rId3"/>
     <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="Coverage" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="77">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -70,36 +71,72 @@
     <t>energy anomaly</t>
   </si>
   <si>
-    <t>CHGNetv0.3.0</t>
+    <t>Allegro-OAM-L</t>
+  </si>
+  <si>
+    <t>AlphaNet-v1-OMA</t>
+  </si>
+  <si>
+    <t>CHGNet-v0.3.0</t>
   </si>
   <si>
     <t>DPA-3.1-3M-FT</t>
   </si>
   <si>
+    <t>DPA-4.0.1-pro-MPtrj</t>
+  </si>
+  <si>
     <t>Eqnorm-MPtrj</t>
   </si>
   <si>
+    <t>EquFlash</t>
+  </si>
+  <si>
+    <t>EquFlashV2</t>
+  </si>
+  <si>
     <t>eSEN-30M-OAM</t>
   </si>
   <si>
     <t>GRACE-2L-OAM</t>
   </si>
   <si>
+    <t>MACE-MH-1-OC20</t>
+  </si>
+  <si>
+    <t>MACE-MH-1-OMAT</t>
+  </si>
+  <si>
     <t>MACE-MPA-0</t>
   </si>
   <si>
-    <t>MATLANTISv8</t>
-  </si>
-  <si>
-    <t>MatterSim_v1_5M</t>
+    <t>MatterSim-v1-5M</t>
+  </si>
+  <si>
+    <t>NequIP-OAM-L</t>
+  </si>
+  <si>
+    <t>NequIP-OAM-XL</t>
+  </si>
+  <si>
+    <t>Nequix-MP-1</t>
   </si>
   <si>
     <t>ORB-v3</t>
   </si>
   <si>
+    <t>PET-OAM-XL</t>
+  </si>
+  <si>
     <t>SevenNet-MF-OMPA</t>
   </si>
   <si>
+    <t>SevenNet-Omni</t>
+  </si>
+  <si>
+    <t>TACE-OAM-L</t>
+  </si>
+  <si>
     <t>Num_normal</t>
   </si>
   <si>
@@ -134,6 +171,84 @@
   </si>
   <si>
     <t>slab_move</t>
+  </si>
+  <si>
+    <t>Num_input</t>
+  </si>
+  <si>
+    <t>Num_succeeded</t>
+  </si>
+  <si>
+    <t>Num_failed</t>
+  </si>
+  <si>
+    <t>Num_not_run</t>
+  </si>
+  <si>
+    <t>Coverage_pct</t>
+  </si>
+  <si>
+    <t>Failed_by_stage</t>
+  </si>
+  <si>
+    <t>catbench_version</t>
+  </si>
+  <si>
+    <t>dispersion</t>
+  </si>
+  <si>
+    <t>device</t>
+  </si>
+  <si>
+    <t>input_md5</t>
+  </si>
+  <si>
+    <t>EqV3-OMatMPtrjSalex</t>
+  </si>
+  <si>
+    <t>MatRIS-10M-OAM</t>
+  </si>
+  <si>
+    <t>UMA-m-1p1-OC20</t>
+  </si>
+  <si>
+    <t>UMA-m-1p1-OMAT</t>
+  </si>
+  <si>
+    <t>UMA-s-1p1-OC20</t>
+  </si>
+  <si>
+    <t>UMA-s-1p1-OMAT</t>
+  </si>
+  <si>
+    <t>UMA-s-1p2-OC20</t>
+  </si>
+  <si>
+    <t>UMA-s-1p2-OC22</t>
+  </si>
+  <si>
+    <t>UMA-s-1p2-OMAT</t>
+  </si>
+  <si>
+    <t>unknown: 417</t>
+  </si>
+  <si>
+    <t>1.1.3</t>
+  </si>
+  <si>
+    <t>1.1.4</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>NVIDIA L40S</t>
+  </si>
+  <si>
+    <t>unknown</t>
+  </si>
+  <si>
+    <t>Num_succeeded counts every computed reaction, including any later excluded by energy_cutoff, so it can exceed Num_total in MLIP_Data.</t>
   </si>
 </sst>
 </file>
@@ -170,7 +285,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -178,11 +293,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -198,6 +328,9 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -493,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.7109375" customWidth="1"/>
@@ -583,49 +716,49 @@
         <v>17</v>
       </c>
       <c r="B3" s="3">
-        <v>78.8968824940048</v>
+        <v>85.61151079136691</v>
       </c>
       <c r="C3" s="3">
-        <v>14.38848920863309</v>
+        <v>9.59232613908873</v>
       </c>
       <c r="D3" s="3">
-        <v>6.71462829736211</v>
+        <v>4.796163069544365</v>
       </c>
       <c r="E3" s="3">
-        <v>3.117505995203837</v>
+        <v>2.398081534772182</v>
       </c>
       <c r="F3" s="3">
-        <v>3.597122302158273</v>
+        <v>2.398081534772182</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.5887254022148928</v>
+        <v>0.481827073604093</v>
       </c>
       <c r="I3" s="4">
-        <v>0.4092730293380338</v>
+        <v>0.2687126015946235</v>
       </c>
       <c r="J3" s="4">
-        <v>0.4580174604468964</v>
+        <v>0.2736540819726366</v>
       </c>
       <c r="K3" s="4">
-        <v>83.64108713029573</v>
+        <v>91.04137098484472</v>
       </c>
       <c r="L3" s="4">
-        <v>79.81662991754357</v>
+        <v>87.16889575587636</v>
       </c>
       <c r="M3" s="5">
         <v>417</v>
       </c>
       <c r="N3" s="5">
-        <v>6221417.308330536</v>
+        <v>841318.4998035431</v>
       </c>
       <c r="O3" s="4">
-        <v>57.19318350353042</v>
+        <v>12.33460151013874</v>
       </c>
       <c r="P3" s="5">
-        <v>108779</v>
+        <v>68208</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="25" customHeight="1">
@@ -633,49 +766,49 @@
         <v>18</v>
       </c>
       <c r="B4" s="3">
-        <v>82.49400479616307</v>
+        <v>88.96882494004797</v>
       </c>
       <c r="C4" s="3">
-        <v>10.31175059952038</v>
+        <v>7.434052757793765</v>
       </c>
       <c r="D4" s="3">
-        <v>7.194244604316546</v>
+        <v>3.597122302158273</v>
       </c>
       <c r="E4" s="3">
-        <v>5.035971223021583</v>
+        <v>1.918465227817746</v>
       </c>
       <c r="F4" s="3">
         <v>1.678657074340528</v>
       </c>
       <c r="G4" s="3">
-        <v>0.4796163069544364</v>
+        <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.5862412854890373</v>
+        <v>0.5173728114623304</v>
       </c>
       <c r="I4" s="4">
-        <v>0.3242764929013701</v>
+        <v>0.3797883914143926</v>
       </c>
       <c r="J4" s="4">
-        <v>0.2693809482732301</v>
+        <v>0.3687704239987323</v>
       </c>
       <c r="K4" s="4">
-        <v>87.99197376792443</v>
+        <v>90.11933310494454</v>
       </c>
       <c r="L4" s="4">
-        <v>84.16732385903299</v>
+        <v>88.4701902907188</v>
       </c>
       <c r="M4" s="5">
         <v>417</v>
       </c>
       <c r="N4" s="5">
-        <v>13846427.45494843</v>
+        <v>1169941.456794739</v>
       </c>
       <c r="O4" s="4">
-        <v>133.8439803478756</v>
+        <v>21.80854969233007</v>
       </c>
       <c r="P4" s="5">
-        <v>103452</v>
+        <v>53646</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="25" customHeight="1">
@@ -683,49 +816,49 @@
         <v>19</v>
       </c>
       <c r="B5" s="3">
-        <v>76.01918465227818</v>
+        <v>82.49400479616307</v>
       </c>
       <c r="C5" s="3">
-        <v>15.10791366906475</v>
+        <v>12.23021582733813</v>
       </c>
       <c r="D5" s="3">
-        <v>8.872901678657074</v>
+        <v>5.275779376498801</v>
       </c>
       <c r="E5" s="3">
-        <v>4.556354916067146</v>
+        <v>3.117505995203837</v>
       </c>
       <c r="F5" s="3">
         <v>1.918465227817746</v>
       </c>
       <c r="G5" s="3">
-        <v>2.398081534772182</v>
+        <v>0.2398081534772182</v>
       </c>
       <c r="H5" s="4">
-        <v>0.6349946099553555</v>
+        <v>0.6094164281019462</v>
       </c>
       <c r="I5" s="4">
-        <v>0.327316527713002</v>
+        <v>0.4396268121650044</v>
       </c>
       <c r="J5" s="4">
-        <v>0.3680796126024997</v>
+        <v>0.4867147170313552</v>
       </c>
       <c r="K5" s="4">
-        <v>86.80639162139676</v>
+        <v>84.29223967764557</v>
       </c>
       <c r="L5" s="4">
-        <v>82.21626725465399</v>
+        <v>81.80207511842707</v>
       </c>
       <c r="M5" s="5">
         <v>417</v>
       </c>
       <c r="N5" s="5">
-        <v>7950150.148630142</v>
+        <v>2880419.574022293</v>
       </c>
       <c r="O5" s="4">
-        <v>86.09929008555771</v>
+        <v>36.21711479684018</v>
       </c>
       <c r="P5" s="5">
-        <v>92337</v>
+        <v>79532</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="25" customHeight="1">
@@ -733,49 +866,49 @@
         <v>20</v>
       </c>
       <c r="B6" s="3">
-        <v>21.58273381294964</v>
+        <v>85.85131894484412</v>
       </c>
       <c r="C6" s="3">
-        <v>11.75059952038369</v>
+        <v>7.673860911270983</v>
       </c>
       <c r="D6" s="3">
-        <v>66.66666666666666</v>
+        <v>6.474820143884892</v>
       </c>
       <c r="E6" s="3">
-        <v>4.07673860911271</v>
+        <v>4.316546762589928</v>
       </c>
       <c r="F6" s="3">
         <v>2.158273381294964</v>
       </c>
       <c r="G6" s="3">
-        <v>60.43165467625899</v>
+        <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>2.987586079229203</v>
+        <v>0.5198133493248468</v>
       </c>
       <c r="I6" s="4">
-        <v>1.500136206330224</v>
+        <v>0.3399175685365742</v>
       </c>
       <c r="J6" s="4">
-        <v>3.358309433458686</v>
+        <v>0.2889043510797195</v>
       </c>
       <c r="K6" s="4">
-        <v>89.41614055694224</v>
+        <v>88.86115597318054</v>
       </c>
       <c r="L6" s="4">
-        <v>84.96625518377098</v>
+        <v>87.2146309797773</v>
       </c>
       <c r="M6" s="5">
         <v>417</v>
       </c>
       <c r="N6" s="5">
-        <v>18098080.95026016</v>
+        <v>7124517.288446426</v>
       </c>
       <c r="O6" s="4">
-        <v>204.1129275859132</v>
+        <v>79.59643035758174</v>
       </c>
       <c r="P6" s="5">
-        <v>88667</v>
+        <v>89508</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="25" customHeight="1">
@@ -783,49 +916,49 @@
         <v>21</v>
       </c>
       <c r="B7" s="3">
-        <v>74.10071942446042</v>
+        <v>87.76978417266187</v>
       </c>
       <c r="C7" s="3">
-        <v>12.23021582733813</v>
+        <v>6.235011990407674</v>
       </c>
       <c r="D7" s="3">
-        <v>13.66906474820144</v>
+        <v>5.995203836930456</v>
       </c>
       <c r="E7" s="3">
-        <v>2.877697841726619</v>
+        <v>3.357314148681055</v>
       </c>
       <c r="F7" s="3">
-        <v>5.515587529976019</v>
+        <v>2.637889688249401</v>
       </c>
       <c r="G7" s="3">
-        <v>5.275779376498801</v>
+        <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>1.233729767935043</v>
+        <v>0.6562698184042838</v>
       </c>
       <c r="I7" s="4">
-        <v>0.8291830071216887</v>
+        <v>0.5217386161385179</v>
       </c>
       <c r="J7" s="4">
-        <v>0.834669961061112</v>
+        <v>0.5399167535188764</v>
       </c>
       <c r="K7" s="4">
-        <v>88.41473759767695</v>
+        <v>88.52713747369445</v>
       </c>
       <c r="L7" s="4">
-        <v>83.11753281938286</v>
+        <v>86.94545035112694</v>
       </c>
       <c r="M7" s="5">
         <v>417</v>
       </c>
       <c r="N7" s="5">
-        <v>1952770.825386047</v>
+        <v>8125455.62505722</v>
       </c>
       <c r="O7" s="4">
-        <v>14.75370453909886</v>
+        <v>97.76042669350331</v>
       </c>
       <c r="P7" s="5">
-        <v>132358</v>
+        <v>83116</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="25" customHeight="1">
@@ -833,49 +966,49 @@
         <v>22</v>
       </c>
       <c r="B8" s="3">
-        <v>81.05515587529976</v>
+        <v>79.61630695443645</v>
       </c>
       <c r="C8" s="3">
-        <v>11.03117505995204</v>
+        <v>9.832134292565947</v>
       </c>
       <c r="D8" s="3">
-        <v>7.913669064748201</v>
+        <v>10.5515587529976</v>
       </c>
       <c r="E8" s="3">
-        <v>3.597122302158273</v>
+        <v>4.07673860911271</v>
       </c>
       <c r="F8" s="3">
-        <v>2.158273381294964</v>
+        <v>3.357314148681055</v>
       </c>
       <c r="G8" s="3">
-        <v>2.158273381294964</v>
+        <v>3.117505995203837</v>
       </c>
       <c r="H8" s="4">
-        <v>0.7820456948975925</v>
+        <v>0.5817431977283763</v>
       </c>
       <c r="I8" s="4">
-        <v>0.6418682363170366</v>
+        <v>0.3475380406501751</v>
       </c>
       <c r="J8" s="4">
-        <v>0.7134278037682723</v>
+        <v>0.4068934891225255</v>
       </c>
       <c r="K8" s="4">
-        <v>88.59288079740277</v>
+        <v>87.24024861743243</v>
       </c>
       <c r="L8" s="4">
-        <v>84.33940096244986</v>
+        <v>85.04691548774166</v>
       </c>
       <c r="M8" s="5">
         <v>417</v>
       </c>
       <c r="N8" s="5">
-        <v>2541804.596662521</v>
+        <v>5248029.837846756</v>
       </c>
       <c r="O8" s="4">
-        <v>30.83778703867178</v>
+        <v>58.42569733976171</v>
       </c>
       <c r="P8" s="5">
-        <v>82425</v>
+        <v>89824</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="25" customHeight="1">
@@ -883,49 +1016,49 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>78.8968824940048</v>
+        <v>85.13189448441247</v>
       </c>
       <c r="C9" s="3">
-        <v>11.99040767386091</v>
+        <v>7.673860911270983</v>
       </c>
       <c r="D9" s="3">
-        <v>9.112709832134293</v>
+        <v>7.194244604316546</v>
       </c>
       <c r="E9" s="3">
-        <v>2.637889688249401</v>
+        <v>4.796163069544365</v>
       </c>
       <c r="F9" s="3">
-        <v>0.4796163069544364</v>
+        <v>2.398081534772182</v>
       </c>
       <c r="G9" s="3">
-        <v>5.995203836930456</v>
+        <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.6835383834054574</v>
+        <v>0.4851083062470465</v>
       </c>
       <c r="I9" s="4">
-        <v>0.3460467048314761</v>
+        <v>0.3256729966671839</v>
       </c>
       <c r="J9" s="4">
-        <v>0.4619682073776853</v>
+        <v>0.3231681964810551</v>
       </c>
       <c r="K9" s="4">
-        <v>85.72611298716127</v>
+        <v>91.03843455847547</v>
       </c>
       <c r="L9" s="4">
-        <v>82.29851018513956</v>
+        <v>87.96096009098493</v>
       </c>
       <c r="M9" s="5">
         <v>417</v>
       </c>
       <c r="N9" s="5">
-        <v>6785507.981300354</v>
+        <v>5545845.396280289</v>
       </c>
       <c r="O9" s="4">
-        <v>105.8746759447707</v>
+        <v>65.47555986682907</v>
       </c>
       <c r="P9" s="5">
-        <v>64090</v>
+        <v>84701</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="25" customHeight="1">
@@ -933,49 +1066,49 @@
         <v>24</v>
       </c>
       <c r="B10" s="3">
-        <v>76.97841726618705</v>
+        <v>84.65227817745803</v>
       </c>
       <c r="C10" s="3">
         <v>8.872901678657074</v>
       </c>
       <c r="D10" s="3">
-        <v>14.14868105515588</v>
+        <v>6.474820143884892</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>3.117505995203837</v>
       </c>
       <c r="F10" s="3">
+        <v>3.117505995203837</v>
+      </c>
+      <c r="G10" s="3">
         <v>0.2398081534772182</v>
       </c>
-      <c r="G10" s="3">
-        <v>13.90887290167866</v>
-      </c>
       <c r="H10" s="4">
-        <v>1.131747573076614</v>
+        <v>0.5640874168224774</v>
       </c>
       <c r="I10" s="4">
-        <v>0.929214014142774</v>
+        <v>0.3551815256777011</v>
       </c>
       <c r="J10" s="4">
-        <v>1.283831697208598</v>
+        <v>0.2994468400791246</v>
       </c>
       <c r="K10" s="4">
-        <v>88.49410267704199</v>
+        <v>90.35905969102267</v>
       </c>
       <c r="L10" s="4">
-        <v>86.00043455168623</v>
+        <v>87.65111400811951</v>
       </c>
       <c r="M10" s="5">
         <v>417</v>
       </c>
       <c r="N10" s="5">
-        <v>1195934.808731079</v>
+        <v>13594837.72873878</v>
       </c>
       <c r="O10" s="4">
-        <v>37.21364186859629</v>
+        <v>153.6869218017453</v>
       </c>
       <c r="P10" s="5">
-        <v>32137</v>
+        <v>88458</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="25" customHeight="1">
@@ -983,49 +1116,49 @@
         <v>25</v>
       </c>
       <c r="B11" s="3">
-        <v>83.69304556354916</v>
+        <v>21.1031175059952</v>
       </c>
       <c r="C11" s="3">
-        <v>13.42925659472422</v>
+        <v>8.15347721822542</v>
       </c>
       <c r="D11" s="3">
-        <v>2.877697841726619</v>
+        <v>70.74340527577938</v>
       </c>
       <c r="E11" s="3">
-        <v>1.678657074340528</v>
+        <v>2.637889688249401</v>
       </c>
       <c r="F11" s="3">
-        <v>0</v>
+        <v>3.117505995203837</v>
       </c>
       <c r="G11" s="3">
-        <v>1.199040767386091</v>
+        <v>64.98800959232614</v>
       </c>
       <c r="H11" s="4">
-        <v>0.7941526505685722</v>
+        <v>3.197702369891849</v>
       </c>
       <c r="I11" s="4">
-        <v>0.7163606572205142</v>
+        <v>1.495239167888555</v>
       </c>
       <c r="J11" s="4">
-        <v>0.8495956890264433</v>
+        <v>3.47815650146312</v>
       </c>
       <c r="K11" s="4">
-        <v>84.43033328439287</v>
+        <v>91.03215386874164</v>
       </c>
       <c r="L11" s="4">
-        <v>82.07077291187071</v>
+        <v>88.3347013664212</v>
       </c>
       <c r="M11" s="5">
         <v>417</v>
       </c>
       <c r="N11" s="5">
-        <v>805230.2625179291</v>
+        <v>8584210.033655167</v>
       </c>
       <c r="O11" s="4">
-        <v>18.04316264492984</v>
+        <v>112.6625460489693</v>
       </c>
       <c r="P11" s="5">
-        <v>44628</v>
+        <v>76194</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="25" customHeight="1">
@@ -1033,49 +1166,649 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>81.77458033573141</v>
+        <v>77.93764988009593</v>
       </c>
       <c r="C12" s="3">
-        <v>13.42925659472422</v>
+        <v>7.913669064748201</v>
       </c>
       <c r="D12" s="3">
+        <v>14.14868105515588</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1.678657074340528</v>
+      </c>
+      <c r="F12" s="3">
+        <v>7.434052757793765</v>
+      </c>
+      <c r="G12" s="3">
+        <v>5.035971223021583</v>
+      </c>
+      <c r="H12" s="4">
+        <v>1.103251663195861</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.8417298838205968</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.8149567966794034</v>
+      </c>
+      <c r="K12" s="4">
+        <v>89.53620776847904</v>
+      </c>
+      <c r="L12" s="4">
+        <v>86.85961298075371</v>
+      </c>
+      <c r="M12" s="5">
+        <v>417</v>
+      </c>
+      <c r="N12" s="5">
+        <v>1052605.714797974</v>
+      </c>
+      <c r="O12" s="4">
+        <v>7.930846309968684</v>
+      </c>
+      <c r="P12" s="5">
+        <v>132723</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>88.2494004796163</v>
+      </c>
+      <c r="C13" s="3">
+        <v>10.31175059952038</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1.43884892086331</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1.199040767386091</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.2398081534772182</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.6133553565313502</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.4598337778554444</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.5294559939967245</v>
+      </c>
+      <c r="K13" s="4">
+        <v>85.37064226170081</v>
+      </c>
+      <c r="L13" s="4">
+        <v>85.62637138611029</v>
+      </c>
+      <c r="M13" s="5">
+        <v>417</v>
+      </c>
+      <c r="N13" s="5">
+        <v>1658053.02977562</v>
+      </c>
+      <c r="O13" s="4">
+        <v>43.46711311510341</v>
+      </c>
+      <c r="P13" s="5">
+        <v>38145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>88.2494004796163</v>
+      </c>
+      <c r="C14" s="3">
+        <v>10.79136690647482</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.9592326139088728</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.4796163069544364</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.2398081534772182</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.2398081534772182</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.6061865197283446</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.4598232843871146</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.5294559939967235</v>
+      </c>
+      <c r="K14" s="4">
+        <v>85.39902771660221</v>
+      </c>
+      <c r="L14" s="4">
+        <v>85.67326004967613</v>
+      </c>
+      <c r="M14" s="5">
+        <v>417</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1640415.876865387</v>
+      </c>
+      <c r="O14" s="4">
+        <v>43.1597526011731</v>
+      </c>
+      <c r="P14" s="5">
+        <v>38008</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>83.45323741007195</v>
+      </c>
+      <c r="C15" s="3">
+        <v>8.15347721822542</v>
+      </c>
+      <c r="D15" s="3">
+        <v>8.393285371702639</v>
+      </c>
+      <c r="E15" s="3">
+        <v>4.07673860911271</v>
+      </c>
+      <c r="F15" s="3">
+        <v>4.316546762589928</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.5064841562894155</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.3120595526156095</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.3200772354325916</v>
+      </c>
+      <c r="K15" s="4">
+        <v>90.94895512161693</v>
+      </c>
+      <c r="L15" s="4">
+        <v>86.71194587953514</v>
+      </c>
+      <c r="M15" s="5">
+        <v>417</v>
+      </c>
+      <c r="N15" s="5">
+        <v>5453164.825439453</v>
+      </c>
+      <c r="O15" s="4">
+        <v>44.3353942782765</v>
+      </c>
+      <c r="P15" s="5">
+        <v>122998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>77.45803357314148</v>
+      </c>
+      <c r="C16" s="3">
+        <v>6.71462829736211</v>
+      </c>
+      <c r="D16" s="3">
+        <v>15.8273381294964</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.2398081534772182</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.2398081534772182</v>
+      </c>
+      <c r="G16" s="3">
+        <v>15.34772182254197</v>
+      </c>
+      <c r="H16" s="4">
+        <v>1.17698079710852</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.9516622754503556</v>
+      </c>
+      <c r="J16" s="4">
+        <v>1.301613596230816</v>
+      </c>
+      <c r="K16" s="4">
+        <v>89.57805184423889</v>
+      </c>
+      <c r="L16" s="4">
+        <v>88.27177184426887</v>
+      </c>
+      <c r="M16" s="5">
+        <v>417</v>
+      </c>
+      <c r="N16" s="5">
+        <v>467472.5291728973</v>
+      </c>
+      <c r="O16" s="4">
+        <v>23.77784990706497</v>
+      </c>
+      <c r="P16" s="5">
+        <v>19660</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>88.96882494004797</v>
+      </c>
+      <c r="C17" s="3">
+        <v>9.112709832134293</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1.918465227817746</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1.199040767386091</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.7194244604316548</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.4355173061414144</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.2601694645878243</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.2430251409841114</v>
+      </c>
+      <c r="K17" s="4">
+        <v>90.52537561787304</v>
+      </c>
+      <c r="L17" s="4">
+        <v>88.44985756361152</v>
+      </c>
+      <c r="M17" s="5">
+        <v>417</v>
+      </c>
+      <c r="N17" s="5">
+        <v>187153.8400650024</v>
+      </c>
+      <c r="O17" s="4">
+        <v>4.930550610279847</v>
+      </c>
+      <c r="P17" s="5">
+        <v>37958</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="25" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="3">
+        <v>86.09112709832134</v>
+      </c>
+      <c r="C18" s="3">
+        <v>7.194244604316546</v>
+      </c>
+      <c r="D18" s="3">
+        <v>6.71462829736211</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1.918465227817746</v>
+      </c>
+      <c r="F18" s="3">
         <v>4.796163069544365</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0.4239027877928329</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0.259827258989683</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0.244160302587881</v>
+      </c>
+      <c r="K18" s="4">
+        <v>90.59397380055137</v>
+      </c>
+      <c r="L18" s="4">
+        <v>88.5087098106729</v>
+      </c>
+      <c r="M18" s="5">
+        <v>417</v>
+      </c>
+      <c r="N18" s="5">
+        <v>743583.1923484802</v>
+      </c>
+      <c r="O18" s="4">
+        <v>7.497914656843466</v>
+      </c>
+      <c r="P18" s="5">
+        <v>99172</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="25" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="3">
+        <v>83.45323741007195</v>
+      </c>
+      <c r="C19" s="3">
+        <v>9.112709832134293</v>
+      </c>
+      <c r="D19" s="3">
+        <v>7.434052757793765</v>
+      </c>
+      <c r="E19" s="3">
+        <v>3.117505995203837</v>
+      </c>
+      <c r="F19" s="3">
         <v>3.357314148681055</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G19" s="3">
+        <v>0.9592326139088728</v>
+      </c>
+      <c r="H19" s="4">
+        <v>0.5413353861779071</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0.3943409726186826</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0.455153623419881</v>
+      </c>
+      <c r="K19" s="4">
+        <v>87.67965219660995</v>
+      </c>
+      <c r="L19" s="4">
+        <v>85.18873491810325</v>
+      </c>
+      <c r="M19" s="5">
+        <v>417</v>
+      </c>
+      <c r="N19" s="5">
+        <v>1879011.90161705</v>
+      </c>
+      <c r="O19" s="4">
+        <v>21.99707216746526</v>
+      </c>
+      <c r="P19" s="5">
+        <v>85421</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="25" customHeight="1">
+      <c r="A20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="3">
+        <v>86.33093525179856</v>
+      </c>
+      <c r="C20" s="3">
+        <v>9.832134292565947</v>
+      </c>
+      <c r="D20" s="3">
+        <v>3.836930455635491</v>
+      </c>
+      <c r="E20" s="3">
         <v>1.43884892086331</v>
       </c>
-      <c r="G12" s="3">
-        <v>0</v>
-      </c>
-      <c r="H12" s="4">
-        <v>0.5699730013891364</v>
-      </c>
-      <c r="I12" s="4">
-        <v>0.3550444013912888</v>
-      </c>
-      <c r="J12" s="4">
-        <v>0.3356500571589113</v>
-      </c>
-      <c r="K12" s="4">
-        <v>89.28652995970567</v>
-      </c>
-      <c r="L12" s="4">
-        <v>84.2652321096143</v>
-      </c>
-      <c r="M12" s="5">
-        <v>417</v>
-      </c>
-      <c r="N12" s="5">
-        <v>5552124.415874481</v>
-      </c>
-      <c r="O12" s="4">
-        <v>72.7613086241512</v>
-      </c>
-      <c r="P12" s="5">
-        <v>76306</v>
+      <c r="F20" s="3">
+        <v>0.7194244604316548</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1.678657074340528</v>
+      </c>
+      <c r="H20" s="4">
+        <v>0.8058413640100689</v>
+      </c>
+      <c r="I20" s="4">
+        <v>0.6991158002394484</v>
+      </c>
+      <c r="J20" s="4">
+        <v>0.8292079152767905</v>
+      </c>
+      <c r="K20" s="4">
+        <v>85.09429191340804</v>
+      </c>
+      <c r="L20" s="4">
+        <v>84.80721463097757</v>
+      </c>
+      <c r="M20" s="5">
+        <v>417</v>
+      </c>
+      <c r="N20" s="5">
+        <v>398424.3714809418</v>
+      </c>
+      <c r="O20" s="4">
+        <v>11.37120758835955</v>
+      </c>
+      <c r="P20" s="5">
+        <v>35038</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="25" customHeight="1">
+      <c r="A21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="3">
+        <v>15.10791366906475</v>
+      </c>
+      <c r="C21" s="3">
+        <v>8.15347721822542</v>
+      </c>
+      <c r="D21" s="3">
+        <v>76.73860911270984</v>
+      </c>
+      <c r="E21" s="3">
+        <v>5.035971223021583</v>
+      </c>
+      <c r="F21" s="3">
+        <v>3.357314148681055</v>
+      </c>
+      <c r="G21" s="3">
+        <v>68.34532374100719</v>
+      </c>
+      <c r="H21" s="4">
+        <v>3.725268119846413</v>
+      </c>
+      <c r="I21" s="4">
+        <v>1.683814446047063</v>
+      </c>
+      <c r="J21" s="4">
+        <v>4.05178104890006</v>
+      </c>
+      <c r="K21" s="4">
+        <v>88.53692556159149</v>
+      </c>
+      <c r="L21" s="4">
+        <v>86.28361740137804</v>
+      </c>
+      <c r="M21" s="5">
+        <v>417</v>
+      </c>
+      <c r="N21" s="5">
+        <v>6848319.43655014</v>
+      </c>
+      <c r="O21" s="4">
+        <v>68.46197115444352</v>
+      </c>
+      <c r="P21" s="5">
+        <v>100031</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="25" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="3">
+        <v>85.85131894484412</v>
+      </c>
+      <c r="C22" s="3">
+        <v>11.03117505995204</v>
+      </c>
+      <c r="D22" s="3">
+        <v>3.117505995203837</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2.158273381294964</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0.9592326139088728</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <v>0.534409958872309</v>
+      </c>
+      <c r="I22" s="4">
+        <v>0.3544776054071484</v>
+      </c>
+      <c r="J22" s="4">
+        <v>0.3314260069439594</v>
+      </c>
+      <c r="K22" s="4">
+        <v>90.07080050245509</v>
+      </c>
+      <c r="L22" s="4">
+        <v>87.31304888974479</v>
+      </c>
+      <c r="M22" s="5">
+        <v>417</v>
+      </c>
+      <c r="N22" s="5">
+        <v>1333879.640579224</v>
+      </c>
+      <c r="O22" s="4">
+        <v>27.04486203806135</v>
+      </c>
+      <c r="P22" s="5">
+        <v>49321</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="25" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="3">
+        <v>86.09112709832134</v>
+      </c>
+      <c r="C23" s="3">
+        <v>9.832134292565947</v>
+      </c>
+      <c r="D23" s="3">
+        <v>4.07673860911271</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2.158273381294964</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1.918465227817746</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <v>0.453860449570709</v>
+      </c>
+      <c r="I23" s="4">
+        <v>0.30118835203792</v>
+      </c>
+      <c r="J23" s="4">
+        <v>0.292367571521976</v>
+      </c>
+      <c r="K23" s="4">
+        <v>89.85848056248868</v>
+      </c>
+      <c r="L23" s="4">
+        <v>87.6878899564886</v>
+      </c>
+      <c r="M23" s="5">
+        <v>417</v>
+      </c>
+      <c r="N23" s="5">
+        <v>1684151.628732681</v>
+      </c>
+      <c r="O23" s="4">
+        <v>27.40418557557734</v>
+      </c>
+      <c r="P23" s="5">
+        <v>61456</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="25" customHeight="1">
+      <c r="A24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="3">
+        <v>88.72901678657075</v>
+      </c>
+      <c r="C24" s="3">
+        <v>9.59232613908873</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1.678657074340528</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1.678657074340528</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <v>0.4523613489462006</v>
+      </c>
+      <c r="I24" s="4">
+        <v>0.2728915448939426</v>
+      </c>
+      <c r="J24" s="4">
+        <v>0.253459500680093</v>
+      </c>
+      <c r="K24" s="4">
+        <v>90.22871498719377</v>
+      </c>
+      <c r="L24" s="4">
+        <v>87.9503108922234</v>
+      </c>
+      <c r="M24" s="5">
+        <v>417</v>
+      </c>
+      <c r="N24" s="5">
+        <v>5087407.732486725</v>
+      </c>
+      <c r="O24" s="4">
+        <v>152.7062203958194</v>
+      </c>
+      <c r="P24" s="5">
+        <v>33315</v>
       </c>
     </row>
   </sheetData>
@@ -1100,7 +1833,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.7109375" customWidth="1"/>
@@ -1190,49 +1923,49 @@
         <v>17</v>
       </c>
       <c r="B3" s="3">
-        <v>78.8968824940048</v>
+        <v>85.37170263788968</v>
       </c>
       <c r="C3" s="3">
-        <v>14.38848920863309</v>
+        <v>9.59232613908873</v>
       </c>
       <c r="D3" s="3">
-        <v>6.71462829736211</v>
+        <v>5.035971223021583</v>
       </c>
       <c r="E3" s="3">
-        <v>3.117505995203837</v>
+        <v>2.398081534772182</v>
       </c>
       <c r="F3" s="3">
-        <v>3.597122302158273</v>
+        <v>2.398081534772182</v>
       </c>
       <c r="G3" s="3">
-        <v>0</v>
+        <v>0.2398081534772182</v>
       </c>
       <c r="H3" s="4">
-        <v>0.4775265588688606</v>
+        <v>0.3757049236141269</v>
       </c>
       <c r="I3" s="4">
-        <v>0.1840150534247423</v>
+        <v>0.1368610286092319</v>
       </c>
       <c r="J3" s="4">
-        <v>0.2416386770104657</v>
+        <v>0.1767204908880148</v>
       </c>
       <c r="K3" s="4">
-        <v>83.64108713029573</v>
+        <v>91.04137098484472</v>
       </c>
       <c r="L3" s="4">
-        <v>79.81662991754357</v>
+        <v>87.16889575587636</v>
       </c>
       <c r="M3" s="5">
         <v>417</v>
       </c>
       <c r="N3" s="5">
-        <v>6221417.308330536</v>
+        <v>841318.4998035431</v>
       </c>
       <c r="O3" s="4">
-        <v>57.19318350353042</v>
+        <v>12.33460151013874</v>
       </c>
       <c r="P3" s="5">
-        <v>108779</v>
+        <v>68208</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="25" customHeight="1">
@@ -1240,49 +1973,49 @@
         <v>18</v>
       </c>
       <c r="B4" s="3">
-        <v>82.01438848920863</v>
+        <v>88.72901678657075</v>
       </c>
       <c r="C4" s="3">
-        <v>10.31175059952038</v>
+        <v>7.434052757793765</v>
       </c>
       <c r="D4" s="3">
-        <v>7.673860911270983</v>
+        <v>3.836930455635491</v>
       </c>
       <c r="E4" s="3">
-        <v>5.035971223021583</v>
+        <v>1.918465227817746</v>
       </c>
       <c r="F4" s="3">
         <v>1.678657074340528</v>
       </c>
       <c r="G4" s="3">
-        <v>0.9592326139088728</v>
+        <v>0.2398081534772182</v>
       </c>
       <c r="H4" s="4">
-        <v>0.4455558579164098</v>
+        <v>0.3500712089905565</v>
       </c>
       <c r="I4" s="4">
-        <v>0.1459713252892462</v>
+        <v>0.1844044584181797</v>
       </c>
       <c r="J4" s="4">
-        <v>0.1669020418580272</v>
+        <v>0.1939099435186237</v>
       </c>
       <c r="K4" s="4">
-        <v>87.99197376792443</v>
+        <v>90.11933310494454</v>
       </c>
       <c r="L4" s="4">
-        <v>84.16732385903299</v>
+        <v>88.4701902907188</v>
       </c>
       <c r="M4" s="5">
         <v>417</v>
       </c>
       <c r="N4" s="5">
-        <v>13846427.45494843</v>
+        <v>1169941.456794739</v>
       </c>
       <c r="O4" s="4">
-        <v>133.8439803478756</v>
+        <v>21.80854969233007</v>
       </c>
       <c r="P4" s="5">
-        <v>103452</v>
+        <v>53646</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="25" customHeight="1">
@@ -1290,16 +2023,16 @@
         <v>19</v>
       </c>
       <c r="B5" s="3">
-        <v>78.17745803357315</v>
+        <v>82.49400479616307</v>
       </c>
       <c r="C5" s="3">
-        <v>15.10791366906475</v>
+        <v>12.23021582733813</v>
       </c>
       <c r="D5" s="3">
-        <v>6.71462829736211</v>
+        <v>5.275779376498801</v>
       </c>
       <c r="E5" s="3">
-        <v>4.556354916067146</v>
+        <v>3.117505995203837</v>
       </c>
       <c r="F5" s="3">
         <v>1.918465227817746</v>
@@ -1308,31 +2041,31 @@
         <v>0.2398081534772182</v>
       </c>
       <c r="H5" s="4">
-        <v>0.5910009363065332</v>
+        <v>0.454897145098236</v>
       </c>
       <c r="I5" s="4">
-        <v>0.2025373476410338</v>
+        <v>0.1782923175955492</v>
       </c>
       <c r="J5" s="4">
-        <v>0.2280553737329047</v>
+        <v>0.2319369745683433</v>
       </c>
       <c r="K5" s="4">
-        <v>86.80639162139676</v>
+        <v>84.29223967764557</v>
       </c>
       <c r="L5" s="4">
-        <v>82.21626725465399</v>
+        <v>81.80207511842707</v>
       </c>
       <c r="M5" s="5">
         <v>417</v>
       </c>
       <c r="N5" s="5">
-        <v>7950150.148630142</v>
+        <v>2880419.574022293</v>
       </c>
       <c r="O5" s="4">
-        <v>86.09929008555771</v>
+        <v>36.21711479684018</v>
       </c>
       <c r="P5" s="5">
-        <v>92337</v>
+        <v>79532</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="25" customHeight="1">
@@ -1340,49 +2073,49 @@
         <v>20</v>
       </c>
       <c r="B6" s="3">
-        <v>81.5347721822542</v>
+        <v>85.61151079136691</v>
       </c>
       <c r="C6" s="3">
-        <v>11.75059952038369</v>
+        <v>7.673860911270983</v>
       </c>
       <c r="D6" s="3">
         <v>6.71462829736211</v>
       </c>
       <c r="E6" s="3">
-        <v>4.07673860911271</v>
+        <v>4.316546762589928</v>
       </c>
       <c r="F6" s="3">
         <v>2.158273381294964</v>
       </c>
       <c r="G6" s="3">
-        <v>0.4796163069544364</v>
+        <v>0.2398081534772182</v>
       </c>
       <c r="H6" s="4">
-        <v>0.4172795168433855</v>
+        <v>0.3647968319484268</v>
       </c>
       <c r="I6" s="4">
-        <v>0.1390380653662679</v>
+        <v>0.1341867326331597</v>
       </c>
       <c r="J6" s="4">
-        <v>0.1672874711017581</v>
+        <v>0.1512549526071609</v>
       </c>
       <c r="K6" s="4">
-        <v>89.41614055694224</v>
+        <v>88.86115597318054</v>
       </c>
       <c r="L6" s="4">
-        <v>84.96625518377098</v>
+        <v>87.2146309797773</v>
       </c>
       <c r="M6" s="5">
         <v>417</v>
       </c>
       <c r="N6" s="5">
-        <v>18098080.95026016</v>
+        <v>7124517.288446426</v>
       </c>
       <c r="O6" s="4">
-        <v>204.1129275859132</v>
+        <v>79.59643035758174</v>
       </c>
       <c r="P6" s="5">
-        <v>88667</v>
+        <v>89508</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="25" customHeight="1">
@@ -1390,49 +2123,49 @@
         <v>21</v>
       </c>
       <c r="B7" s="3">
-        <v>78.8968824940048</v>
+        <v>87.29016786570743</v>
       </c>
       <c r="C7" s="3">
-        <v>12.23021582733813</v>
+        <v>6.235011990407674</v>
       </c>
       <c r="D7" s="3">
-        <v>8.872901678657074</v>
+        <v>6.474820143884892</v>
       </c>
       <c r="E7" s="3">
-        <v>2.877697841726619</v>
+        <v>3.357314148681055</v>
       </c>
       <c r="F7" s="3">
-        <v>5.515587529976019</v>
+        <v>2.637889688249401</v>
       </c>
       <c r="G7" s="3">
         <v>0.4796163069544364</v>
       </c>
       <c r="H7" s="4">
-        <v>0.4743183470732041</v>
+        <v>0.3768920249086029</v>
       </c>
       <c r="I7" s="4">
-        <v>0.176170441236133</v>
+        <v>0.1788743704781029</v>
       </c>
       <c r="J7" s="4">
-        <v>0.2488362365797424</v>
+        <v>0.2209511349781866</v>
       </c>
       <c r="K7" s="4">
-        <v>88.41473759767695</v>
+        <v>88.52713747369445</v>
       </c>
       <c r="L7" s="4">
-        <v>83.11753281938286</v>
+        <v>86.94545035112694</v>
       </c>
       <c r="M7" s="5">
         <v>417</v>
       </c>
       <c r="N7" s="5">
-        <v>1952770.825386047</v>
+        <v>8125455.62505722</v>
       </c>
       <c r="O7" s="4">
-        <v>14.75370453909886</v>
+        <v>97.76042669350331</v>
       </c>
       <c r="P7" s="5">
-        <v>132358</v>
+        <v>83116</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="25" customHeight="1">
@@ -1440,49 +2173,49 @@
         <v>22</v>
       </c>
       <c r="B8" s="3">
-        <v>83.21342925659472</v>
+        <v>82.49400479616307</v>
       </c>
       <c r="C8" s="3">
-        <v>11.03117505995204</v>
+        <v>9.832134292565947</v>
       </c>
       <c r="D8" s="3">
-        <v>5.755395683453238</v>
+        <v>7.673860911270983</v>
       </c>
       <c r="E8" s="3">
-        <v>3.597122302158273</v>
+        <v>4.07673860911271</v>
       </c>
       <c r="F8" s="3">
-        <v>2.158273381294964</v>
+        <v>3.357314148681055</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
+        <v>0.2398081534772182</v>
       </c>
       <c r="H8" s="4">
-        <v>0.4924873936994161</v>
+        <v>0.4697355655702001</v>
       </c>
       <c r="I8" s="4">
-        <v>0.2322557762421205</v>
+        <v>0.208436782201467</v>
       </c>
       <c r="J8" s="4">
-        <v>0.2435211029628517</v>
+        <v>0.2235443557582992</v>
       </c>
       <c r="K8" s="4">
-        <v>88.59288079740277</v>
+        <v>87.24024861743243</v>
       </c>
       <c r="L8" s="4">
-        <v>84.33940096244986</v>
+        <v>85.04691548774166</v>
       </c>
       <c r="M8" s="5">
         <v>417</v>
       </c>
       <c r="N8" s="5">
-        <v>2541804.596662521</v>
+        <v>5248029.837846756</v>
       </c>
       <c r="O8" s="4">
-        <v>30.83778703867178</v>
+        <v>58.42569733976171</v>
       </c>
       <c r="P8" s="5">
-        <v>82425</v>
+        <v>89824</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="25" customHeight="1">
@@ -1490,49 +2223,49 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>84.41247002398082</v>
+        <v>84.89208633093526</v>
       </c>
       <c r="C9" s="3">
-        <v>11.99040767386091</v>
+        <v>7.673860911270983</v>
       </c>
       <c r="D9" s="3">
-        <v>3.597122302158273</v>
+        <v>7.434052757793765</v>
       </c>
       <c r="E9" s="3">
-        <v>2.637889688249401</v>
+        <v>4.796163069544365</v>
       </c>
       <c r="F9" s="3">
-        <v>0.4796163069544364</v>
+        <v>2.398081534772182</v>
       </c>
       <c r="G9" s="3">
-        <v>0.4796163069544364</v>
+        <v>0.2398081534772182</v>
       </c>
       <c r="H9" s="4">
-        <v>0.4262459759711521</v>
+        <v>0.356557538803959</v>
       </c>
       <c r="I9" s="4">
-        <v>0.1782157774966955</v>
+        <v>0.1336373456245595</v>
       </c>
       <c r="J9" s="4">
-        <v>0.2089196318028229</v>
+        <v>0.1598632634064003</v>
       </c>
       <c r="K9" s="4">
-        <v>85.72611298716127</v>
+        <v>91.03843455847547</v>
       </c>
       <c r="L9" s="4">
-        <v>82.29851018513956</v>
+        <v>87.96096009098493</v>
       </c>
       <c r="M9" s="5">
         <v>417</v>
       </c>
       <c r="N9" s="5">
-        <v>6785507.981300354</v>
+        <v>5545845.396280289</v>
       </c>
       <c r="O9" s="4">
-        <v>105.8746759447707</v>
+        <v>65.47555986682907</v>
       </c>
       <c r="P9" s="5">
-        <v>64090</v>
+        <v>84701</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="25" customHeight="1">
@@ -1540,49 +2273,49 @@
         <v>24</v>
       </c>
       <c r="B10" s="3">
-        <v>87.29016786570743</v>
+        <v>84.41247002398082</v>
       </c>
       <c r="C10" s="3">
         <v>8.872901678657074</v>
       </c>
       <c r="D10" s="3">
-        <v>3.836930455635491</v>
+        <v>6.71462829736211</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>3.117505995203837</v>
       </c>
       <c r="F10" s="3">
-        <v>0.2398081534772182</v>
+        <v>3.117505995203837</v>
       </c>
       <c r="G10" s="3">
-        <v>3.597122302158273</v>
+        <v>0.4796163069544364</v>
       </c>
       <c r="H10" s="4">
-        <v>0.453930553698761</v>
+        <v>0.3546036201944233</v>
       </c>
       <c r="I10" s="4">
-        <v>0.2436839305189714</v>
+        <v>0.1074869888808368</v>
       </c>
       <c r="J10" s="4">
-        <v>0.3126886552883324</v>
+        <v>0.1340692645607101</v>
       </c>
       <c r="K10" s="4">
-        <v>88.49410267704199</v>
+        <v>90.35905969102267</v>
       </c>
       <c r="L10" s="4">
-        <v>86.00043455168623</v>
+        <v>87.65111400811951</v>
       </c>
       <c r="M10" s="5">
         <v>417</v>
       </c>
       <c r="N10" s="5">
-        <v>1195934.808731079</v>
+        <v>13594837.72873878</v>
       </c>
       <c r="O10" s="4">
-        <v>37.21364186859629</v>
+        <v>153.6869218017453</v>
       </c>
       <c r="P10" s="5">
-        <v>32137</v>
+        <v>88458</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="25" customHeight="1">
@@ -1590,49 +2323,49 @@
         <v>25</v>
       </c>
       <c r="B11" s="3">
-        <v>84.65227817745803</v>
+        <v>85.85131894484412</v>
       </c>
       <c r="C11" s="3">
-        <v>13.42925659472422</v>
+        <v>8.15347721822542</v>
       </c>
       <c r="D11" s="3">
-        <v>1.918465227817746</v>
+        <v>5.995203836930456</v>
       </c>
       <c r="E11" s="3">
-        <v>1.678657074340528</v>
+        <v>2.637889688249401</v>
       </c>
       <c r="F11" s="3">
-        <v>0</v>
+        <v>3.117505995203837</v>
       </c>
       <c r="G11" s="3">
         <v>0.2398081534772182</v>
       </c>
       <c r="H11" s="4">
-        <v>0.4342044297613155</v>
+        <v>0.3498803879190556</v>
       </c>
       <c r="I11" s="4">
-        <v>0.2254113615991279</v>
+        <v>0.1276563708763963</v>
       </c>
       <c r="J11" s="4">
-        <v>0.2345600822361193</v>
+        <v>0.1565683761074726</v>
       </c>
       <c r="K11" s="4">
-        <v>84.43033328439287</v>
+        <v>91.03215386874164</v>
       </c>
       <c r="L11" s="4">
-        <v>82.07077291187071</v>
+        <v>88.3347013664212</v>
       </c>
       <c r="M11" s="5">
         <v>417</v>
       </c>
       <c r="N11" s="5">
-        <v>805230.2625179291</v>
+        <v>8584210.033655167</v>
       </c>
       <c r="O11" s="4">
-        <v>18.04316264492984</v>
+        <v>112.6625460489693</v>
       </c>
       <c r="P11" s="5">
-        <v>44628</v>
+        <v>76194</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="25" customHeight="1">
@@ -1640,49 +2373,649 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>81.29496402877699</v>
+        <v>82.25419664268586</v>
       </c>
       <c r="C12" s="3">
-        <v>13.42925659472422</v>
+        <v>7.913669064748201</v>
       </c>
       <c r="D12" s="3">
-        <v>5.275779376498801</v>
+        <v>9.832134292565947</v>
       </c>
       <c r="E12" s="3">
+        <v>1.678657074340528</v>
+      </c>
+      <c r="F12" s="3">
+        <v>7.434052757793765</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.7194244604316548</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.3702848514625932</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1413615288962222</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.2424746761302281</v>
+      </c>
+      <c r="K12" s="4">
+        <v>89.53620776847904</v>
+      </c>
+      <c r="L12" s="4">
+        <v>86.85961298075371</v>
+      </c>
+      <c r="M12" s="5">
+        <v>417</v>
+      </c>
+      <c r="N12" s="5">
+        <v>1052605.714797974</v>
+      </c>
+      <c r="O12" s="4">
+        <v>7.930846309968684</v>
+      </c>
+      <c r="P12" s="5">
+        <v>132723</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>88.2494004796163</v>
+      </c>
+      <c r="C13" s="3">
+        <v>10.31175059952038</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1.43884892086331</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1.199040767386091</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.2398081534772182</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.3878360558249886</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1629219401736822</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.176186435651746</v>
+      </c>
+      <c r="K13" s="4">
+        <v>85.37064226170081</v>
+      </c>
+      <c r="L13" s="4">
+        <v>85.62637138611029</v>
+      </c>
+      <c r="M13" s="5">
+        <v>417</v>
+      </c>
+      <c r="N13" s="5">
+        <v>1658053.02977562</v>
+      </c>
+      <c r="O13" s="4">
+        <v>43.46711311510341</v>
+      </c>
+      <c r="P13" s="5">
+        <v>38145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>88.2494004796163</v>
+      </c>
+      <c r="C14" s="3">
+        <v>10.79136690647482</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.9592326139088728</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.4796163069544364</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.2398081534772182</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.2398081534772182</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.3825545717100727</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.1629324336731964</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.1761864356517463</v>
+      </c>
+      <c r="K14" s="4">
+        <v>85.39902771660221</v>
+      </c>
+      <c r="L14" s="4">
+        <v>85.67326004967613</v>
+      </c>
+      <c r="M14" s="5">
+        <v>417</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1640415.876865387</v>
+      </c>
+      <c r="O14" s="4">
+        <v>43.1597526011731</v>
+      </c>
+      <c r="P14" s="5">
+        <v>38008</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>83.45323741007195</v>
+      </c>
+      <c r="C15" s="3">
+        <v>8.15347721822542</v>
+      </c>
+      <c r="D15" s="3">
+        <v>8.393285371702639</v>
+      </c>
+      <c r="E15" s="3">
+        <v>4.07673860911271</v>
+      </c>
+      <c r="F15" s="3">
+        <v>4.316546762589928</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.4060160097403402</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.1589377362225276</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.2143768254896939</v>
+      </c>
+      <c r="K15" s="4">
+        <v>90.94895512161693</v>
+      </c>
+      <c r="L15" s="4">
+        <v>86.71194587953514</v>
+      </c>
+      <c r="M15" s="5">
+        <v>417</v>
+      </c>
+      <c r="N15" s="5">
+        <v>5453164.825439453</v>
+      </c>
+      <c r="O15" s="4">
+        <v>44.3353942782765</v>
+      </c>
+      <c r="P15" s="5">
+        <v>122998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>89.68824940047962</v>
+      </c>
+      <c r="C16" s="3">
+        <v>6.71462829736211</v>
+      </c>
+      <c r="D16" s="3">
+        <v>3.597122302158273</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.2398081534772182</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.2398081534772182</v>
+      </c>
+      <c r="G16" s="3">
+        <v>3.117505995203837</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.4072313171866569</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.2422882676793329</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.3007191062708913</v>
+      </c>
+      <c r="K16" s="4">
+        <v>89.57805184423889</v>
+      </c>
+      <c r="L16" s="4">
+        <v>88.27177184426887</v>
+      </c>
+      <c r="M16" s="5">
+        <v>417</v>
+      </c>
+      <c r="N16" s="5">
+        <v>467472.5291728973</v>
+      </c>
+      <c r="O16" s="4">
+        <v>23.77784990706497</v>
+      </c>
+      <c r="P16" s="5">
+        <v>19660</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>88.72901678657075</v>
+      </c>
+      <c r="C17" s="3">
+        <v>9.112709832134293</v>
+      </c>
+      <c r="D17" s="3">
+        <v>2.158273381294964</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1.199040767386091</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.7194244604316548</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.2398081534772182</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.316709074553564</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.128475943234266</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.1389658309696781</v>
+      </c>
+      <c r="K17" s="4">
+        <v>90.52537561787304</v>
+      </c>
+      <c r="L17" s="4">
+        <v>88.44985756361152</v>
+      </c>
+      <c r="M17" s="5">
+        <v>417</v>
+      </c>
+      <c r="N17" s="5">
+        <v>187153.8400650024</v>
+      </c>
+      <c r="O17" s="4">
+        <v>4.930550610279847</v>
+      </c>
+      <c r="P17" s="5">
+        <v>37958</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="25" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="3">
+        <v>85.85131894484412</v>
+      </c>
+      <c r="C18" s="3">
+        <v>7.194244604316546</v>
+      </c>
+      <c r="D18" s="3">
+        <v>6.954436450839328</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1.918465227817746</v>
+      </c>
+      <c r="F18" s="3">
+        <v>4.796163069544365</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0.2398081534772182</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0.3153666141882343</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0.1225912568824734</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0.1462353420636407</v>
+      </c>
+      <c r="K18" s="4">
+        <v>90.59397380055137</v>
+      </c>
+      <c r="L18" s="4">
+        <v>88.5087098106729</v>
+      </c>
+      <c r="M18" s="5">
+        <v>417</v>
+      </c>
+      <c r="N18" s="5">
+        <v>743583.1923484802</v>
+      </c>
+      <c r="O18" s="4">
+        <v>7.497914656843466</v>
+      </c>
+      <c r="P18" s="5">
+        <v>99172</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="25" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="3">
+        <v>84.17266187050359</v>
+      </c>
+      <c r="C19" s="3">
+        <v>9.112709832134293</v>
+      </c>
+      <c r="D19" s="3">
+        <v>6.71462829736211</v>
+      </c>
+      <c r="E19" s="3">
+        <v>3.117505995203837</v>
+      </c>
+      <c r="F19" s="3">
         <v>3.357314148681055</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G19" s="3">
+        <v>0.2398081534772182</v>
+      </c>
+      <c r="H19" s="4">
+        <v>0.4178624032779714</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0.2080122070707578</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0.2346331772510117</v>
+      </c>
+      <c r="K19" s="4">
+        <v>87.67965219660995</v>
+      </c>
+      <c r="L19" s="4">
+        <v>85.18873491810325</v>
+      </c>
+      <c r="M19" s="5">
+        <v>417</v>
+      </c>
+      <c r="N19" s="5">
+        <v>1879011.90161705</v>
+      </c>
+      <c r="O19" s="4">
+        <v>21.99707216746526</v>
+      </c>
+      <c r="P19" s="5">
+        <v>85421</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="25" customHeight="1">
+      <c r="A20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="3">
+        <v>87.52997601918466</v>
+      </c>
+      <c r="C20" s="3">
+        <v>9.832134292565947</v>
+      </c>
+      <c r="D20" s="3">
+        <v>2.637889688249401</v>
+      </c>
+      <c r="E20" s="3">
         <v>1.43884892086331</v>
       </c>
-      <c r="G12" s="3">
+      <c r="F20" s="3">
+        <v>0.7194244604316548</v>
+      </c>
+      <c r="G20" s="3">
         <v>0.4796163069544364</v>
       </c>
-      <c r="H12" s="4">
-        <v>0.4077414919969667</v>
-      </c>
-      <c r="I12" s="4">
-        <v>0.1547182178750684</v>
-      </c>
-      <c r="J12" s="4">
-        <v>0.1796730984415253</v>
-      </c>
-      <c r="K12" s="4">
-        <v>89.28652995970567</v>
-      </c>
-      <c r="L12" s="4">
-        <v>84.2652321096143</v>
-      </c>
-      <c r="M12" s="5">
-        <v>417</v>
-      </c>
-      <c r="N12" s="5">
-        <v>5552124.415874481</v>
-      </c>
-      <c r="O12" s="4">
-        <v>72.7613086241512</v>
-      </c>
-      <c r="P12" s="5">
-        <v>76306</v>
+      <c r="H20" s="4">
+        <v>0.4219277992845096</v>
+      </c>
+      <c r="I20" s="4">
+        <v>0.2008033477894901</v>
+      </c>
+      <c r="J20" s="4">
+        <v>0.1952287675290391</v>
+      </c>
+      <c r="K20" s="4">
+        <v>85.09429191340804</v>
+      </c>
+      <c r="L20" s="4">
+        <v>84.80721463097757</v>
+      </c>
+      <c r="M20" s="5">
+        <v>417</v>
+      </c>
+      <c r="N20" s="5">
+        <v>398424.3714809418</v>
+      </c>
+      <c r="O20" s="4">
+        <v>11.37120758835955</v>
+      </c>
+      <c r="P20" s="5">
+        <v>35038</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="25" customHeight="1">
+      <c r="A21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="3">
+        <v>83.21342925659472</v>
+      </c>
+      <c r="C21" s="3">
+        <v>8.15347721822542</v>
+      </c>
+      <c r="D21" s="3">
+        <v>8.633093525179856</v>
+      </c>
+      <c r="E21" s="3">
+        <v>5.035971223021583</v>
+      </c>
+      <c r="F21" s="3">
+        <v>3.357314148681055</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0.2398081534772182</v>
+      </c>
+      <c r="H21" s="4">
+        <v>0.3840682323728851</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0.1397852249155717</v>
+      </c>
+      <c r="J21" s="4">
+        <v>0.192407225115782</v>
+      </c>
+      <c r="K21" s="4">
+        <v>88.53692556159149</v>
+      </c>
+      <c r="L21" s="4">
+        <v>86.28361740137804</v>
+      </c>
+      <c r="M21" s="5">
+        <v>417</v>
+      </c>
+      <c r="N21" s="5">
+        <v>6848319.43655014</v>
+      </c>
+      <c r="O21" s="4">
+        <v>68.46197115444352</v>
+      </c>
+      <c r="P21" s="5">
+        <v>100031</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="25" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="3">
+        <v>85.61151079136691</v>
+      </c>
+      <c r="C22" s="3">
+        <v>11.03117505995204</v>
+      </c>
+      <c r="D22" s="3">
+        <v>3.357314148681055</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2.158273381294964</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0.9592326139088728</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0.2398081534772182</v>
+      </c>
+      <c r="H22" s="4">
+        <v>0.3536816766549096</v>
+      </c>
+      <c r="I22" s="4">
+        <v>0.1419213643724826</v>
+      </c>
+      <c r="J22" s="4">
+        <v>0.1667222816516311</v>
+      </c>
+      <c r="K22" s="4">
+        <v>90.07080050245509</v>
+      </c>
+      <c r="L22" s="4">
+        <v>87.31304888974479</v>
+      </c>
+      <c r="M22" s="5">
+        <v>417</v>
+      </c>
+      <c r="N22" s="5">
+        <v>1333879.640579224</v>
+      </c>
+      <c r="O22" s="4">
+        <v>27.04486203806135</v>
+      </c>
+      <c r="P22" s="5">
+        <v>49321</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="25" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="3">
+        <v>85.85131894484412</v>
+      </c>
+      <c r="C23" s="3">
+        <v>9.832134292565947</v>
+      </c>
+      <c r="D23" s="3">
+        <v>4.316546762589928</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2.158273381294964</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1.918465227817746</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0.2398081534772182</v>
+      </c>
+      <c r="H23" s="4">
+        <v>0.3141409035060697</v>
+      </c>
+      <c r="I23" s="4">
+        <v>0.1320853697047388</v>
+      </c>
+      <c r="J23" s="4">
+        <v>0.1547547469474103</v>
+      </c>
+      <c r="K23" s="4">
+        <v>89.85848056248868</v>
+      </c>
+      <c r="L23" s="4">
+        <v>87.6878899564886</v>
+      </c>
+      <c r="M23" s="5">
+        <v>417</v>
+      </c>
+      <c r="N23" s="5">
+        <v>1684151.628732681</v>
+      </c>
+      <c r="O23" s="4">
+        <v>27.40418557557734</v>
+      </c>
+      <c r="P23" s="5">
+        <v>61456</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="25" customHeight="1">
+      <c r="A24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="3">
+        <v>88.48920863309353</v>
+      </c>
+      <c r="C24" s="3">
+        <v>9.59232613908873</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1.918465227817746</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1.678657074340528</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0.2398081534772182</v>
+      </c>
+      <c r="H24" s="4">
+        <v>0.3413872435393266</v>
+      </c>
+      <c r="I24" s="4">
+        <v>0.1461872600512379</v>
+      </c>
+      <c r="J24" s="4">
+        <v>0.1618483907394722</v>
+      </c>
+      <c r="K24" s="4">
+        <v>90.22871498719377</v>
+      </c>
+      <c r="L24" s="4">
+        <v>87.9503108922234</v>
+      </c>
+      <c r="M24" s="5">
+        <v>417</v>
+      </c>
+      <c r="N24" s="5">
+        <v>5087407.732486725</v>
+      </c>
+      <c r="O24" s="4">
+        <v>152.7062203958194</v>
+      </c>
+      <c r="P24" s="5">
+        <v>33315</v>
       </c>
     </row>
   </sheetData>
@@ -1707,7 +3040,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1726,24 +3059,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -1766,25 +3099,25 @@
         <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="25" customHeight="1">
@@ -1792,34 +3125,34 @@
         <v>17</v>
       </c>
       <c r="B3" s="5">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="C3" s="5">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D3" s="5">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E3" s="5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F3" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G3" s="5">
         <v>0</v>
       </c>
       <c r="H3" s="5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I3" s="5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L3" s="5">
         <v>0</v>
@@ -1836,28 +3169,28 @@
         <v>18</v>
       </c>
       <c r="B4" s="5">
-        <v>344</v>
+        <v>371</v>
       </c>
       <c r="C4" s="5">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D4" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E4" s="5">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F4" s="5">
         <v>7</v>
       </c>
       <c r="G4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" s="5">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I4" s="5">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -1880,34 +3213,34 @@
         <v>19</v>
       </c>
       <c r="B5" s="5">
-        <v>317</v>
+        <v>344</v>
       </c>
       <c r="C5" s="5">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D5" s="5">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E5" s="5">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F5" s="5">
         <v>8</v>
       </c>
       <c r="G5" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H5" s="5">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I5" s="5">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
@@ -1916,7 +3249,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="25" customHeight="1">
@@ -1924,28 +3257,28 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <v>90</v>
+        <v>358</v>
       </c>
       <c r="C6" s="5">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D6" s="5">
-        <v>278</v>
+        <v>27</v>
       </c>
       <c r="E6" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="5">
         <v>9</v>
       </c>
       <c r="G6" s="5">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="H6" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6" s="5">
         <v>0</v>
@@ -1968,34 +3301,34 @@
         <v>21</v>
       </c>
       <c r="B7" s="5">
-        <v>309</v>
+        <v>366</v>
       </c>
       <c r="C7" s="5">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="D7" s="5">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="E7" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F7" s="5">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G7" s="5">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H7" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I7" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J7" s="5">
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="L7" s="5">
         <v>0</v>
@@ -2012,43 +3345,43 @@
         <v>22</v>
       </c>
       <c r="B8" s="5">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C8" s="5">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D8" s="5">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E8" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F8" s="5">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G8" s="5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H8" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I8" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J8" s="5">
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L8" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
       </c>
       <c r="N8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="25" customHeight="1">
@@ -2056,34 +3389,34 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>329</v>
+        <v>355</v>
       </c>
       <c r="C9" s="5">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D9" s="5">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E9" s="5">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F9" s="5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G9" s="5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H9" s="5">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I9" s="5">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J9" s="5">
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L9" s="5">
         <v>0</v>
@@ -2100,34 +3433,34 @@
         <v>24</v>
       </c>
       <c r="B10" s="5">
-        <v>321</v>
+        <v>353</v>
       </c>
       <c r="C10" s="5">
         <v>37</v>
       </c>
       <c r="D10" s="5">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="E10" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F10" s="5">
+        <v>13</v>
+      </c>
+      <c r="G10" s="5">
         <v>1</v>
       </c>
-      <c r="G10" s="5">
-        <v>58</v>
-      </c>
       <c r="H10" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I10" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J10" s="5">
         <v>0</v>
       </c>
       <c r="K10" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L10" s="5">
         <v>0</v>
@@ -2136,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="25" customHeight="1">
@@ -2144,34 +3477,34 @@
         <v>25</v>
       </c>
       <c r="B11" s="5">
-        <v>349</v>
+        <v>88</v>
       </c>
       <c r="C11" s="5">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="D11" s="5">
-        <v>12</v>
+        <v>295</v>
       </c>
       <c r="E11" s="5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F11" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G11" s="5">
-        <v>5</v>
+        <v>271</v>
       </c>
       <c r="H11" s="5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I11" s="5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J11" s="5">
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L11" s="5">
         <v>0</v>
@@ -2188,42 +3521,570 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="C12" s="5">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="D12" s="5">
+        <v>59</v>
+      </c>
+      <c r="E12" s="5">
+        <v>7</v>
+      </c>
+      <c r="F12" s="5">
+        <v>31</v>
+      </c>
+      <c r="G12" s="5">
+        <v>21</v>
+      </c>
+      <c r="H12" s="5">
+        <v>7</v>
+      </c>
+      <c r="I12" s="5">
+        <v>7</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>31</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>368</v>
+      </c>
+      <c r="C13" s="5">
+        <v>43</v>
+      </c>
+      <c r="D13" s="5">
+        <v>6</v>
+      </c>
+      <c r="E13" s="5">
+        <v>5</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5">
+        <v>5</v>
+      </c>
+      <c r="I13" s="5">
+        <v>5</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>368</v>
+      </c>
+      <c r="C14" s="5">
+        <v>45</v>
+      </c>
+      <c r="D14" s="5">
+        <v>4</v>
+      </c>
+      <c r="E14" s="5">
+        <v>2</v>
+      </c>
+      <c r="F14" s="5">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5">
+        <v>2</v>
+      </c>
+      <c r="I14" s="5">
+        <v>2</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>1</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>348</v>
+      </c>
+      <c r="C15" s="5">
+        <v>34</v>
+      </c>
+      <c r="D15" s="5">
+        <v>35</v>
+      </c>
+      <c r="E15" s="5">
+        <v>17</v>
+      </c>
+      <c r="F15" s="5">
+        <v>18</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>17</v>
+      </c>
+      <c r="I15" s="5">
+        <v>17</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>18</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>323</v>
+      </c>
+      <c r="C16" s="5">
+        <v>28</v>
+      </c>
+      <c r="D16" s="5">
+        <v>66</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5">
+        <v>64</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>371</v>
+      </c>
+      <c r="C17" s="5">
+        <v>38</v>
+      </c>
+      <c r="D17" s="5">
+        <v>8</v>
+      </c>
+      <c r="E17" s="5">
+        <v>5</v>
+      </c>
+      <c r="F17" s="5">
+        <v>3</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>5</v>
+      </c>
+      <c r="I17" s="5">
+        <v>5</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>3</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="25" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="5">
+        <v>359</v>
+      </c>
+      <c r="C18" s="5">
+        <v>30</v>
+      </c>
+      <c r="D18" s="5">
+        <v>28</v>
+      </c>
+      <c r="E18" s="5">
+        <v>8</v>
+      </c>
+      <c r="F18" s="5">
         <v>20</v>
       </c>
-      <c r="E12" s="5">
+      <c r="G18" s="5">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5">
+        <v>8</v>
+      </c>
+      <c r="I18" s="5">
+        <v>8</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5">
+        <v>20</v>
+      </c>
+      <c r="L18" s="5">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="25" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="5">
+        <v>348</v>
+      </c>
+      <c r="C19" s="5">
+        <v>38</v>
+      </c>
+      <c r="D19" s="5">
+        <v>31</v>
+      </c>
+      <c r="E19" s="5">
+        <v>13</v>
+      </c>
+      <c r="F19" s="5">
         <v>14</v>
       </c>
-      <c r="F12" s="5">
+      <c r="G19" s="5">
+        <v>4</v>
+      </c>
+      <c r="H19" s="5">
+        <v>13</v>
+      </c>
+      <c r="I19" s="5">
+        <v>13</v>
+      </c>
+      <c r="J19" s="5">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5">
+        <v>8</v>
+      </c>
+      <c r="L19" s="5">
+        <v>4</v>
+      </c>
+      <c r="M19" s="5">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="25" customHeight="1">
+      <c r="A20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="5">
+        <v>360</v>
+      </c>
+      <c r="C20" s="5">
+        <v>41</v>
+      </c>
+      <c r="D20" s="5">
+        <v>16</v>
+      </c>
+      <c r="E20" s="5">
         <v>6</v>
       </c>
-      <c r="G12" s="5">
-        <v>0</v>
-      </c>
-      <c r="H12" s="5">
+      <c r="F20" s="5">
+        <v>3</v>
+      </c>
+      <c r="G20" s="5">
+        <v>7</v>
+      </c>
+      <c r="H20" s="5">
+        <v>6</v>
+      </c>
+      <c r="I20" s="5">
+        <v>6</v>
+      </c>
+      <c r="J20" s="5">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5">
+        <v>3</v>
+      </c>
+      <c r="L20" s="5">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="25" customHeight="1">
+      <c r="A21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="5">
+        <v>63</v>
+      </c>
+      <c r="C21" s="5">
+        <v>34</v>
+      </c>
+      <c r="D21" s="5">
+        <v>320</v>
+      </c>
+      <c r="E21" s="5">
+        <v>21</v>
+      </c>
+      <c r="F21" s="5">
         <v>14</v>
       </c>
-      <c r="I12" s="5">
+      <c r="G21" s="5">
+        <v>285</v>
+      </c>
+      <c r="H21" s="5">
+        <v>21</v>
+      </c>
+      <c r="I21" s="5">
+        <v>21</v>
+      </c>
+      <c r="J21" s="5">
+        <v>0</v>
+      </c>
+      <c r="K21" s="5">
         <v>14</v>
       </c>
-      <c r="J12" s="5">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5">
-        <v>6</v>
-      </c>
-      <c r="L12" s="5">
-        <v>0</v>
-      </c>
-      <c r="M12" s="5">
-        <v>0</v>
-      </c>
-      <c r="N12" s="5">
+      <c r="L21" s="5">
+        <v>0</v>
+      </c>
+      <c r="M21" s="5">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="25" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="5">
+        <v>358</v>
+      </c>
+      <c r="C22" s="5">
+        <v>46</v>
+      </c>
+      <c r="D22" s="5">
+        <v>13</v>
+      </c>
+      <c r="E22" s="5">
+        <v>9</v>
+      </c>
+      <c r="F22" s="5">
+        <v>4</v>
+      </c>
+      <c r="G22" s="5">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5">
+        <v>9</v>
+      </c>
+      <c r="I22" s="5">
+        <v>9</v>
+      </c>
+      <c r="J22" s="5">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5">
+        <v>4</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="25" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="5">
+        <v>359</v>
+      </c>
+      <c r="C23" s="5">
+        <v>41</v>
+      </c>
+      <c r="D23" s="5">
+        <v>17</v>
+      </c>
+      <c r="E23" s="5">
+        <v>9</v>
+      </c>
+      <c r="F23" s="5">
+        <v>8</v>
+      </c>
+      <c r="G23" s="5">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5">
+        <v>9</v>
+      </c>
+      <c r="I23" s="5">
+        <v>9</v>
+      </c>
+      <c r="J23" s="5">
+        <v>0</v>
+      </c>
+      <c r="K23" s="5">
+        <v>8</v>
+      </c>
+      <c r="L23" s="5">
+        <v>0</v>
+      </c>
+      <c r="M23" s="5">
+        <v>0</v>
+      </c>
+      <c r="N23" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="25" customHeight="1">
+      <c r="A24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="5">
+        <v>370</v>
+      </c>
+      <c r="C24" s="5">
+        <v>40</v>
+      </c>
+      <c r="D24" s="5">
+        <v>7</v>
+      </c>
+      <c r="E24" s="5">
+        <v>7</v>
+      </c>
+      <c r="F24" s="5">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5">
+        <v>7</v>
+      </c>
+      <c r="I24" s="5">
+        <v>7</v>
+      </c>
+      <c r="J24" s="5">
+        <v>0</v>
+      </c>
+      <c r="K24" s="5">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5">
+        <v>0</v>
+      </c>
+      <c r="M24" s="5">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5">
         <v>0</v>
       </c>
     </row>
@@ -2242,7 +4103,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2261,24 +4122,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -2301,25 +4162,25 @@
         <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="25" customHeight="1">
@@ -2327,34 +4188,34 @@
         <v>17</v>
       </c>
       <c r="B3" s="5">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="C3" s="5">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D3" s="5">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E3" s="5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F3" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I3" s="5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L3" s="5">
         <v>0</v>
@@ -2371,28 +4232,28 @@
         <v>18</v>
       </c>
       <c r="B4" s="5">
-        <v>342</v>
+        <v>370</v>
       </c>
       <c r="C4" s="5">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D4" s="5">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E4" s="5">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F4" s="5">
         <v>7</v>
       </c>
       <c r="G4" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H4" s="5">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I4" s="5">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2415,16 +4276,16 @@
         <v>19</v>
       </c>
       <c r="B5" s="5">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="C5" s="5">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D5" s="5">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E5" s="5">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F5" s="5">
         <v>8</v>
@@ -2433,16 +4294,16 @@
         <v>1</v>
       </c>
       <c r="H5" s="5">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I5" s="5">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
@@ -2451,7 +4312,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="25" customHeight="1">
@@ -2459,28 +4320,28 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="C6" s="5">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D6" s="5">
         <v>28</v>
       </c>
       <c r="E6" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="5">
         <v>9</v>
       </c>
       <c r="G6" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6" s="5">
         <v>0</v>
@@ -2503,34 +4364,34 @@
         <v>21</v>
       </c>
       <c r="B7" s="5">
-        <v>329</v>
+        <v>364</v>
       </c>
       <c r="C7" s="5">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="D7" s="5">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E7" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F7" s="5">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
       </c>
       <c r="H7" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I7" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J7" s="5">
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="L7" s="5">
         <v>0</v>
@@ -2547,43 +4408,43 @@
         <v>22</v>
       </c>
       <c r="B8" s="5">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C8" s="5">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D8" s="5">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E8" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F8" s="5">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I8" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J8" s="5">
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L8" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
       </c>
       <c r="N8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="25" customHeight="1">
@@ -2591,34 +4452,34 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C9" s="5">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D9" s="5">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E9" s="5">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F9" s="5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G9" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="5">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I9" s="5">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J9" s="5">
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L9" s="5">
         <v>0</v>
@@ -2635,34 +4496,34 @@
         <v>24</v>
       </c>
       <c r="B10" s="5">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="C10" s="5">
         <v>37</v>
       </c>
       <c r="D10" s="5">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E10" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F10" s="5">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G10" s="5">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H10" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I10" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J10" s="5">
         <v>0</v>
       </c>
       <c r="K10" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L10" s="5">
         <v>0</v>
@@ -2671,7 +4532,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="25" customHeight="1">
@@ -2679,34 +4540,34 @@
         <v>25</v>
       </c>
       <c r="B11" s="5">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C11" s="5">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="D11" s="5">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E11" s="5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F11" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G11" s="5">
         <v>1</v>
       </c>
       <c r="H11" s="5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I11" s="5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J11" s="5">
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L11" s="5">
         <v>0</v>
@@ -2723,42 +4584,570 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C12" s="5">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="D12" s="5">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E12" s="5">
+        <v>7</v>
+      </c>
+      <c r="F12" s="5">
+        <v>31</v>
+      </c>
+      <c r="G12" s="5">
+        <v>3</v>
+      </c>
+      <c r="H12" s="5">
+        <v>7</v>
+      </c>
+      <c r="I12" s="5">
+        <v>7</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>31</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>368</v>
+      </c>
+      <c r="C13" s="5">
+        <v>43</v>
+      </c>
+      <c r="D13" s="5">
+        <v>6</v>
+      </c>
+      <c r="E13" s="5">
+        <v>5</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5">
+        <v>5</v>
+      </c>
+      <c r="I13" s="5">
+        <v>5</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>368</v>
+      </c>
+      <c r="C14" s="5">
+        <v>45</v>
+      </c>
+      <c r="D14" s="5">
+        <v>4</v>
+      </c>
+      <c r="E14" s="5">
+        <v>2</v>
+      </c>
+      <c r="F14" s="5">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5">
+        <v>2</v>
+      </c>
+      <c r="I14" s="5">
+        <v>2</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>1</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>348</v>
+      </c>
+      <c r="C15" s="5">
+        <v>34</v>
+      </c>
+      <c r="D15" s="5">
+        <v>35</v>
+      </c>
+      <c r="E15" s="5">
+        <v>17</v>
+      </c>
+      <c r="F15" s="5">
+        <v>18</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>17</v>
+      </c>
+      <c r="I15" s="5">
+        <v>17</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>18</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>374</v>
+      </c>
+      <c r="C16" s="5">
+        <v>28</v>
+      </c>
+      <c r="D16" s="5">
+        <v>15</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5">
+        <v>13</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>370</v>
+      </c>
+      <c r="C17" s="5">
+        <v>38</v>
+      </c>
+      <c r="D17" s="5">
+        <v>9</v>
+      </c>
+      <c r="E17" s="5">
+        <v>5</v>
+      </c>
+      <c r="F17" s="5">
+        <v>3</v>
+      </c>
+      <c r="G17" s="5">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5">
+        <v>5</v>
+      </c>
+      <c r="I17" s="5">
+        <v>5</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>3</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="25" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="5">
+        <v>358</v>
+      </c>
+      <c r="C18" s="5">
+        <v>30</v>
+      </c>
+      <c r="D18" s="5">
+        <v>29</v>
+      </c>
+      <c r="E18" s="5">
+        <v>8</v>
+      </c>
+      <c r="F18" s="5">
+        <v>20</v>
+      </c>
+      <c r="G18" s="5">
+        <v>1</v>
+      </c>
+      <c r="H18" s="5">
+        <v>8</v>
+      </c>
+      <c r="I18" s="5">
+        <v>8</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5">
+        <v>20</v>
+      </c>
+      <c r="L18" s="5">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="25" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="5">
+        <v>351</v>
+      </c>
+      <c r="C19" s="5">
+        <v>38</v>
+      </c>
+      <c r="D19" s="5">
+        <v>28</v>
+      </c>
+      <c r="E19" s="5">
+        <v>13</v>
+      </c>
+      <c r="F19" s="5">
         <v>14</v>
       </c>
-      <c r="F12" s="5">
+      <c r="G19" s="5">
+        <v>1</v>
+      </c>
+      <c r="H19" s="5">
+        <v>13</v>
+      </c>
+      <c r="I19" s="5">
+        <v>13</v>
+      </c>
+      <c r="J19" s="5">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5">
+        <v>8</v>
+      </c>
+      <c r="L19" s="5">
+        <v>4</v>
+      </c>
+      <c r="M19" s="5">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="25" customHeight="1">
+      <c r="A20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="5">
+        <v>365</v>
+      </c>
+      <c r="C20" s="5">
+        <v>41</v>
+      </c>
+      <c r="D20" s="5">
+        <v>11</v>
+      </c>
+      <c r="E20" s="5">
         <v>6</v>
       </c>
-      <c r="G12" s="5">
+      <c r="F20" s="5">
+        <v>3</v>
+      </c>
+      <c r="G20" s="5">
         <v>2</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H20" s="5">
+        <v>6</v>
+      </c>
+      <c r="I20" s="5">
+        <v>6</v>
+      </c>
+      <c r="J20" s="5">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5">
+        <v>3</v>
+      </c>
+      <c r="L20" s="5">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="25" customHeight="1">
+      <c r="A21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="5">
+        <v>347</v>
+      </c>
+      <c r="C21" s="5">
+        <v>34</v>
+      </c>
+      <c r="D21" s="5">
+        <v>36</v>
+      </c>
+      <c r="E21" s="5">
+        <v>21</v>
+      </c>
+      <c r="F21" s="5">
         <v>14</v>
       </c>
-      <c r="I12" s="5">
+      <c r="G21" s="5">
+        <v>1</v>
+      </c>
+      <c r="H21" s="5">
+        <v>21</v>
+      </c>
+      <c r="I21" s="5">
+        <v>21</v>
+      </c>
+      <c r="J21" s="5">
+        <v>0</v>
+      </c>
+      <c r="K21" s="5">
         <v>14</v>
       </c>
-      <c r="J12" s="5">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5">
-        <v>6</v>
-      </c>
-      <c r="L12" s="5">
-        <v>0</v>
-      </c>
-      <c r="M12" s="5">
-        <v>0</v>
-      </c>
-      <c r="N12" s="5">
+      <c r="L21" s="5">
+        <v>0</v>
+      </c>
+      <c r="M21" s="5">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="25" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="5">
+        <v>357</v>
+      </c>
+      <c r="C22" s="5">
+        <v>46</v>
+      </c>
+      <c r="D22" s="5">
+        <v>14</v>
+      </c>
+      <c r="E22" s="5">
+        <v>9</v>
+      </c>
+      <c r="F22" s="5">
+        <v>4</v>
+      </c>
+      <c r="G22" s="5">
+        <v>1</v>
+      </c>
+      <c r="H22" s="5">
+        <v>9</v>
+      </c>
+      <c r="I22" s="5">
+        <v>9</v>
+      </c>
+      <c r="J22" s="5">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5">
+        <v>4</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="25" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="5">
+        <v>358</v>
+      </c>
+      <c r="C23" s="5">
+        <v>41</v>
+      </c>
+      <c r="D23" s="5">
+        <v>18</v>
+      </c>
+      <c r="E23" s="5">
+        <v>9</v>
+      </c>
+      <c r="F23" s="5">
+        <v>8</v>
+      </c>
+      <c r="G23" s="5">
+        <v>1</v>
+      </c>
+      <c r="H23" s="5">
+        <v>9</v>
+      </c>
+      <c r="I23" s="5">
+        <v>9</v>
+      </c>
+      <c r="J23" s="5">
+        <v>0</v>
+      </c>
+      <c r="K23" s="5">
+        <v>8</v>
+      </c>
+      <c r="L23" s="5">
+        <v>0</v>
+      </c>
+      <c r="M23" s="5">
+        <v>0</v>
+      </c>
+      <c r="N23" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="25" customHeight="1">
+      <c r="A24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="5">
+        <v>369</v>
+      </c>
+      <c r="C24" s="5">
+        <v>40</v>
+      </c>
+      <c r="D24" s="5">
+        <v>8</v>
+      </c>
+      <c r="E24" s="5">
+        <v>7</v>
+      </c>
+      <c r="F24" s="5">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5">
+        <v>1</v>
+      </c>
+      <c r="H24" s="5">
+        <v>7</v>
+      </c>
+      <c r="I24" s="5">
+        <v>7</v>
+      </c>
+      <c r="J24" s="5">
+        <v>0</v>
+      </c>
+      <c r="K24" s="5">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5">
+        <v>0</v>
+      </c>
+      <c r="M24" s="5">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5">
         <v>0</v>
       </c>
     </row>
@@ -2773,4 +5162,1073 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K34"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>417</v>
+      </c>
+      <c r="C2">
+        <v>417</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+      <c r="H2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>417</v>
+      </c>
+      <c r="C3">
+        <v>417</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>100</v>
+      </c>
+      <c r="H3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>417</v>
+      </c>
+      <c r="C4">
+        <v>417</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="H4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J4" t="s">
+        <v>74</v>
+      </c>
+      <c r="K4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>417</v>
+      </c>
+      <c r="C5">
+        <v>417</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="H5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
+        <v>417</v>
+      </c>
+      <c r="C6">
+        <v>417</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="H6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I6" t="s">
+        <v>73</v>
+      </c>
+      <c r="J6" t="s">
+        <v>74</v>
+      </c>
+      <c r="K6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
+        <v>417</v>
+      </c>
+      <c r="C7">
+        <v>417</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="H7" t="s">
+        <v>71</v>
+      </c>
+      <c r="I7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J7" t="s">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8">
+        <v>417</v>
+      </c>
+      <c r="C8">
+        <v>417</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="H8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I8" t="s">
+        <v>73</v>
+      </c>
+      <c r="J8" t="s">
+        <v>74</v>
+      </c>
+      <c r="K8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
+        <v>417</v>
+      </c>
+      <c r="C9">
+        <v>417</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="H9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10">
+        <v>417</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>417</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10" t="s">
+        <v>73</v>
+      </c>
+      <c r="J10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <v>417</v>
+      </c>
+      <c r="C11">
+        <v>417</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>100</v>
+      </c>
+      <c r="H11" t="s">
+        <v>71</v>
+      </c>
+      <c r="I11" t="s">
+        <v>73</v>
+      </c>
+      <c r="J11" t="s">
+        <v>74</v>
+      </c>
+      <c r="K11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12">
+        <v>417</v>
+      </c>
+      <c r="C12">
+        <v>417</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>100</v>
+      </c>
+      <c r="H12" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12" t="s">
+        <v>73</v>
+      </c>
+      <c r="J12" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13">
+        <v>417</v>
+      </c>
+      <c r="C13">
+        <v>417</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>100</v>
+      </c>
+      <c r="H13" t="s">
+        <v>71</v>
+      </c>
+      <c r="I13" t="s">
+        <v>73</v>
+      </c>
+      <c r="J13" t="s">
+        <v>74</v>
+      </c>
+      <c r="K13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14">
+        <v>417</v>
+      </c>
+      <c r="C14">
+        <v>417</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>100</v>
+      </c>
+      <c r="H14" t="s">
+        <v>71</v>
+      </c>
+      <c r="I14" t="s">
+        <v>73</v>
+      </c>
+      <c r="J14" t="s">
+        <v>74</v>
+      </c>
+      <c r="K14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15">
+        <v>417</v>
+      </c>
+      <c r="C15">
+        <v>417</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>100</v>
+      </c>
+      <c r="H15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15" t="s">
+        <v>73</v>
+      </c>
+      <c r="J15" t="s">
+        <v>74</v>
+      </c>
+      <c r="K15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16">
+        <v>417</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>417</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" t="s">
+        <v>71</v>
+      </c>
+      <c r="I16" t="s">
+        <v>73</v>
+      </c>
+      <c r="J16" t="s">
+        <v>74</v>
+      </c>
+      <c r="K16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17">
+        <v>417</v>
+      </c>
+      <c r="C17">
+        <v>417</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>100</v>
+      </c>
+      <c r="H17" t="s">
+        <v>71</v>
+      </c>
+      <c r="I17" t="s">
+        <v>73</v>
+      </c>
+      <c r="J17" t="s">
+        <v>74</v>
+      </c>
+      <c r="K17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18">
+        <v>417</v>
+      </c>
+      <c r="C18">
+        <v>417</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>100</v>
+      </c>
+      <c r="H18" t="s">
+        <v>71</v>
+      </c>
+      <c r="I18" t="s">
+        <v>73</v>
+      </c>
+      <c r="J18" t="s">
+        <v>74</v>
+      </c>
+      <c r="K18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19">
+        <v>417</v>
+      </c>
+      <c r="C19">
+        <v>417</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>100</v>
+      </c>
+      <c r="H19" t="s">
+        <v>71</v>
+      </c>
+      <c r="I19" t="s">
+        <v>73</v>
+      </c>
+      <c r="J19" t="s">
+        <v>74</v>
+      </c>
+      <c r="K19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20">
+        <v>417</v>
+      </c>
+      <c r="C20">
+        <v>417</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>100</v>
+      </c>
+      <c r="H20" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20" t="s">
+        <v>73</v>
+      </c>
+      <c r="J20" t="s">
+        <v>74</v>
+      </c>
+      <c r="K20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21">
+        <v>417</v>
+      </c>
+      <c r="C21">
+        <v>417</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>100</v>
+      </c>
+      <c r="H21" t="s">
+        <v>71</v>
+      </c>
+      <c r="I21" t="s">
+        <v>73</v>
+      </c>
+      <c r="J21" t="s">
+        <v>74</v>
+      </c>
+      <c r="K21" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22">
+        <v>417</v>
+      </c>
+      <c r="C22">
+        <v>417</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>100</v>
+      </c>
+      <c r="H22" t="s">
+        <v>72</v>
+      </c>
+      <c r="I22" t="s">
+        <v>73</v>
+      </c>
+      <c r="J22" t="s">
+        <v>74</v>
+      </c>
+      <c r="K22" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23">
+        <v>417</v>
+      </c>
+      <c r="C23">
+        <v>417</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>100</v>
+      </c>
+      <c r="H23" t="s">
+        <v>71</v>
+      </c>
+      <c r="I23" t="s">
+        <v>73</v>
+      </c>
+      <c r="J23" t="s">
+        <v>74</v>
+      </c>
+      <c r="K23" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24">
+        <v>417</v>
+      </c>
+      <c r="C24">
+        <v>417</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>100</v>
+      </c>
+      <c r="H24" t="s">
+        <v>71</v>
+      </c>
+      <c r="I24" t="s">
+        <v>73</v>
+      </c>
+      <c r="J24" t="s">
+        <v>74</v>
+      </c>
+      <c r="K24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25">
+        <v>417</v>
+      </c>
+      <c r="C25">
+        <v>417</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>100</v>
+      </c>
+      <c r="H25" t="s">
+        <v>71</v>
+      </c>
+      <c r="I25" t="s">
+        <v>73</v>
+      </c>
+      <c r="J25" t="s">
+        <v>74</v>
+      </c>
+      <c r="K25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26">
+        <v>417</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>417</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" t="s">
+        <v>70</v>
+      </c>
+      <c r="H26" t="s">
+        <v>71</v>
+      </c>
+      <c r="I26" t="s">
+        <v>73</v>
+      </c>
+      <c r="J26" t="s">
+        <v>74</v>
+      </c>
+      <c r="K26" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27">
+        <v>417</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>417</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27" t="s">
+        <v>70</v>
+      </c>
+      <c r="H27" t="s">
+        <v>71</v>
+      </c>
+      <c r="I27" t="s">
+        <v>73</v>
+      </c>
+      <c r="J27" t="s">
+        <v>74</v>
+      </c>
+      <c r="K27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28">
+        <v>417</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>417</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28" t="s">
+        <v>70</v>
+      </c>
+      <c r="H28" t="s">
+        <v>71</v>
+      </c>
+      <c r="I28" t="s">
+        <v>73</v>
+      </c>
+      <c r="J28" t="s">
+        <v>74</v>
+      </c>
+      <c r="K28" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29">
+        <v>417</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>417</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" t="s">
+        <v>70</v>
+      </c>
+      <c r="H29" t="s">
+        <v>71</v>
+      </c>
+      <c r="I29" t="s">
+        <v>73</v>
+      </c>
+      <c r="J29" t="s">
+        <v>74</v>
+      </c>
+      <c r="K29" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30">
+        <v>417</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>417</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30" t="s">
+        <v>70</v>
+      </c>
+      <c r="H30" t="s">
+        <v>71</v>
+      </c>
+      <c r="I30" t="s">
+        <v>73</v>
+      </c>
+      <c r="J30" t="s">
+        <v>74</v>
+      </c>
+      <c r="K30" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31">
+        <v>417</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>417</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31" t="s">
+        <v>70</v>
+      </c>
+      <c r="H31" t="s">
+        <v>71</v>
+      </c>
+      <c r="I31" t="s">
+        <v>73</v>
+      </c>
+      <c r="J31" t="s">
+        <v>74</v>
+      </c>
+      <c r="K31" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32">
+        <v>417</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>417</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32" t="s">
+        <v>70</v>
+      </c>
+      <c r="H32" t="s">
+        <v>71</v>
+      </c>
+      <c r="I32" t="s">
+        <v>73</v>
+      </c>
+      <c r="J32" t="s">
+        <v>74</v>
+      </c>
+      <c r="K32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>